--- a/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CD067C-3488-4F17-ACCB-2B42F1397571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF63DB5-C5EC-4EB6-806D-ACEFF84AC6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5737,7 +5737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF05919-9F66-4AA3-A35E-835A899766C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867A1EAA-62B4-44E9-8BA2-3E81FDFC2FDF}">
   <dimension ref="B3:H76"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF63DB5-C5EC-4EB6-806D-ACEFF84AC6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1ACD82-EBD4-44DD-92CA-269CF94AEAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5737,7 +5737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867A1EAA-62B4-44E9-8BA2-3E81FDFC2FDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BE7A0D1-8128-4C71-ABEE-CABF544E17C0}">
   <dimension ref="B3:H76"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1ACD82-EBD4-44DD-92CA-269CF94AEAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659AE2E7-0663-4CB2-A330-3CC598EDC8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5737,7 +5737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BE7A0D1-8128-4C71-ABEE-CABF544E17C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27150595-683E-48B5-AD32-C15FFC9F93F6}">
   <dimension ref="B3:H76"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659AE2E7-0663-4CB2-A330-3CC598EDC8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB049D7-949A-4D0E-A952-0F62C6775831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1271,232 +1271,232 @@
     <t>grid node -- sol9</t>
   </si>
   <si>
-    <t>e_wof44</t>
-  </si>
-  <si>
-    <t>grid node -- wof44</t>
-  </si>
-  <si>
-    <t>e_wof45</t>
-  </si>
-  <si>
-    <t>grid node -- wof45</t>
-  </si>
-  <si>
-    <t>e_wof46</t>
-  </si>
-  <si>
-    <t>grid node -- wof46</t>
-  </si>
-  <si>
-    <t>e_wof47</t>
-  </si>
-  <si>
-    <t>grid node -- wof47</t>
-  </si>
-  <si>
-    <t>e_wof48</t>
-  </si>
-  <si>
-    <t>grid node -- wof48</t>
-  </si>
-  <si>
-    <t>e_wof49</t>
-  </si>
-  <si>
-    <t>grid node -- wof49</t>
-  </si>
-  <si>
-    <t>e_wof50</t>
-  </si>
-  <si>
-    <t>grid node -- wof50</t>
-  </si>
-  <si>
-    <t>e_wof51</t>
-  </si>
-  <si>
-    <t>grid node -- wof51</t>
-  </si>
-  <si>
-    <t>e_wof52</t>
-  </si>
-  <si>
-    <t>grid node -- wof52</t>
-  </si>
-  <si>
-    <t>e_wof53</t>
-  </si>
-  <si>
-    <t>grid node -- wof53</t>
-  </si>
-  <si>
-    <t>e_wof54</t>
-  </si>
-  <si>
-    <t>grid node -- wof54</t>
-  </si>
-  <si>
-    <t>e_wof55</t>
-  </si>
-  <si>
-    <t>grid node -- wof55</t>
-  </si>
-  <si>
-    <t>e_wof56</t>
-  </si>
-  <si>
-    <t>grid node -- wof56</t>
-  </si>
-  <si>
-    <t>e_wof57</t>
-  </si>
-  <si>
-    <t>grid node -- wof57</t>
-  </si>
-  <si>
-    <t>e_wof58</t>
-  </si>
-  <si>
-    <t>grid node -- wof58</t>
-  </si>
-  <si>
-    <t>e_wof59</t>
-  </si>
-  <si>
-    <t>grid node -- wof59</t>
-  </si>
-  <si>
-    <t>e_wof60</t>
-  </si>
-  <si>
-    <t>grid node -- wof60</t>
-  </si>
-  <si>
-    <t>e_wof61</t>
-  </si>
-  <si>
-    <t>grid node -- wof61</t>
-  </si>
-  <si>
-    <t>e_wof62</t>
-  </si>
-  <si>
-    <t>grid node -- wof62</t>
-  </si>
-  <si>
-    <t>e_won25</t>
-  </si>
-  <si>
-    <t>grid node -- won25</t>
-  </si>
-  <si>
-    <t>e_won26</t>
-  </si>
-  <si>
-    <t>grid node -- won26</t>
-  </si>
-  <si>
-    <t>e_won27</t>
-  </si>
-  <si>
-    <t>grid node -- won27</t>
-  </si>
-  <si>
-    <t>e_won28</t>
-  </si>
-  <si>
-    <t>grid node -- won28</t>
-  </si>
-  <si>
-    <t>e_won29</t>
-  </si>
-  <si>
-    <t>grid node -- won29</t>
-  </si>
-  <si>
-    <t>e_won30</t>
-  </si>
-  <si>
-    <t>grid node -- won30</t>
-  </si>
-  <si>
-    <t>e_won31</t>
-  </si>
-  <si>
-    <t>grid node -- won31</t>
-  </si>
-  <si>
-    <t>e_won32</t>
-  </si>
-  <si>
-    <t>grid node -- won32</t>
-  </si>
-  <si>
-    <t>e_won33</t>
-  </si>
-  <si>
-    <t>grid node -- won33</t>
-  </si>
-  <si>
-    <t>e_won34</t>
-  </si>
-  <si>
-    <t>grid node -- won34</t>
-  </si>
-  <si>
-    <t>e_won35</t>
-  </si>
-  <si>
-    <t>grid node -- won35</t>
-  </si>
-  <si>
-    <t>e_won36</t>
-  </si>
-  <si>
-    <t>grid node -- won36</t>
-  </si>
-  <si>
-    <t>e_won37</t>
-  </si>
-  <si>
-    <t>grid node -- won37</t>
-  </si>
-  <si>
-    <t>e_won38</t>
-  </si>
-  <si>
-    <t>grid node -- won38</t>
-  </si>
-  <si>
-    <t>e_won39</t>
-  </si>
-  <si>
-    <t>grid node -- won39</t>
-  </si>
-  <si>
-    <t>e_won40</t>
-  </si>
-  <si>
-    <t>grid node -- won40</t>
-  </si>
-  <si>
-    <t>e_won41</t>
-  </si>
-  <si>
-    <t>grid node -- won41</t>
-  </si>
-  <si>
-    <t>e_won42</t>
-  </si>
-  <si>
-    <t>grid node -- won42</t>
-  </si>
-  <si>
-    <t>e_won43</t>
-  </si>
-  <si>
-    <t>grid node -- won43</t>
+    <t>e_wof1</t>
+  </si>
+  <si>
+    <t>grid node -- wof1</t>
+  </si>
+  <si>
+    <t>e_wof10</t>
+  </si>
+  <si>
+    <t>grid node -- wof10</t>
+  </si>
+  <si>
+    <t>e_wof11</t>
+  </si>
+  <si>
+    <t>grid node -- wof11</t>
+  </si>
+  <si>
+    <t>e_wof12</t>
+  </si>
+  <si>
+    <t>grid node -- wof12</t>
+  </si>
+  <si>
+    <t>e_wof13</t>
+  </si>
+  <si>
+    <t>grid node -- wof13</t>
+  </si>
+  <si>
+    <t>e_wof14</t>
+  </si>
+  <si>
+    <t>grid node -- wof14</t>
+  </si>
+  <si>
+    <t>e_wof15</t>
+  </si>
+  <si>
+    <t>grid node -- wof15</t>
+  </si>
+  <si>
+    <t>e_wof16</t>
+  </si>
+  <si>
+    <t>grid node -- wof16</t>
+  </si>
+  <si>
+    <t>e_wof17</t>
+  </si>
+  <si>
+    <t>grid node -- wof17</t>
+  </si>
+  <si>
+    <t>e_wof18</t>
+  </si>
+  <si>
+    <t>grid node -- wof18</t>
+  </si>
+  <si>
+    <t>e_wof19</t>
+  </si>
+  <si>
+    <t>grid node -- wof19</t>
+  </si>
+  <si>
+    <t>e_wof2</t>
+  </si>
+  <si>
+    <t>grid node -- wof2</t>
+  </si>
+  <si>
+    <t>e_wof3</t>
+  </si>
+  <si>
+    <t>grid node -- wof3</t>
+  </si>
+  <si>
+    <t>e_wof4</t>
+  </si>
+  <si>
+    <t>grid node -- wof4</t>
+  </si>
+  <si>
+    <t>e_wof5</t>
+  </si>
+  <si>
+    <t>grid node -- wof5</t>
+  </si>
+  <si>
+    <t>e_wof6</t>
+  </si>
+  <si>
+    <t>grid node -- wof6</t>
+  </si>
+  <si>
+    <t>e_wof7</t>
+  </si>
+  <si>
+    <t>grid node -- wof7</t>
+  </si>
+  <si>
+    <t>e_wof8</t>
+  </si>
+  <si>
+    <t>grid node -- wof8</t>
+  </si>
+  <si>
+    <t>e_wof9</t>
+  </si>
+  <si>
+    <t>grid node -- wof9</t>
+  </si>
+  <si>
+    <t>e_won1</t>
+  </si>
+  <si>
+    <t>grid node -- won1</t>
+  </si>
+  <si>
+    <t>e_won10</t>
+  </si>
+  <si>
+    <t>grid node -- won10</t>
+  </si>
+  <si>
+    <t>e_won11</t>
+  </si>
+  <si>
+    <t>grid node -- won11</t>
+  </si>
+  <si>
+    <t>e_won12</t>
+  </si>
+  <si>
+    <t>grid node -- won12</t>
+  </si>
+  <si>
+    <t>e_won13</t>
+  </si>
+  <si>
+    <t>grid node -- won13</t>
+  </si>
+  <si>
+    <t>e_won14</t>
+  </si>
+  <si>
+    <t>grid node -- won14</t>
+  </si>
+  <si>
+    <t>e_won15</t>
+  </si>
+  <si>
+    <t>grid node -- won15</t>
+  </si>
+  <si>
+    <t>e_won16</t>
+  </si>
+  <si>
+    <t>grid node -- won16</t>
+  </si>
+  <si>
+    <t>e_won17</t>
+  </si>
+  <si>
+    <t>grid node -- won17</t>
+  </si>
+  <si>
+    <t>e_won18</t>
+  </si>
+  <si>
+    <t>grid node -- won18</t>
+  </si>
+  <si>
+    <t>e_won19</t>
+  </si>
+  <si>
+    <t>grid node -- won19</t>
+  </si>
+  <si>
+    <t>e_won2</t>
+  </si>
+  <si>
+    <t>grid node -- won2</t>
+  </si>
+  <si>
+    <t>e_won3</t>
+  </si>
+  <si>
+    <t>grid node -- won3</t>
+  </si>
+  <si>
+    <t>e_won4</t>
+  </si>
+  <si>
+    <t>grid node -- won4</t>
+  </si>
+  <si>
+    <t>e_won5</t>
+  </si>
+  <si>
+    <t>grid node -- won5</t>
+  </si>
+  <si>
+    <t>e_won6</t>
+  </si>
+  <si>
+    <t>grid node -- won6</t>
+  </si>
+  <si>
+    <t>e_won7</t>
+  </si>
+  <si>
+    <t>grid node -- won7</t>
+  </si>
+  <si>
+    <t>e_won8</t>
+  </si>
+  <si>
+    <t>grid node -- won8</t>
+  </si>
+  <si>
+    <t>e_won9</t>
+  </si>
+  <si>
+    <t>grid node -- won9</t>
   </si>
 </sst>
 </file>
@@ -5737,7 +5737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27150595-683E-48B5-AD32-C15FFC9F93F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B6C0E2-F75F-485F-9226-27E83C6EE49E}">
   <dimension ref="B3:H76"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB049D7-949A-4D0E-A952-0F62C6775831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B979E2-F747-4BE2-8020-6097C1EE95B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5737,7 +5737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B6C0E2-F75F-485F-9226-27E83C6EE49E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E31CFD8-6161-4421-9BC9-87C8B264FA7A}">
   <dimension ref="B3:H76"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B979E2-F747-4BE2-8020-6097C1EE95B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB560A60-0BCB-4C77-9E1B-D2FBAE86D01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5737,7 +5737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E31CFD8-6161-4421-9BC9-87C8B264FA7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9A06E4-412A-4C05-820B-C1A5950F8318}">
   <dimension ref="B3:H76"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
